--- a/data/trans_orig/P33B_R4-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P33B_R4-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>86968</t>
+          <t>97303</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>70046</t>
+          <t>80752</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>106982</t>
+          <t>120466</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>154495</t>
+          <t>169548</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>137964</t>
+          <t>150749</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>172436</t>
+          <t>186715</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>241463</t>
+          <t>266851</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>215310</t>
+          <t>238699</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>267072</t>
+          <t>293694</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>547444</t>
+          <t>592325</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>527430</t>
+          <t>569162</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>564366</t>
+          <t>608876</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>520468</t>
+          <t>562759</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>502527</t>
+          <t>545592</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>536999</t>
+          <t>581558</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1067912</t>
+          <t>1155083</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1042303</t>
+          <t>1128240</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1094065</t>
+          <t>1183235</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,21%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>674963</t>
+          <t>732307</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>674963</t>
+          <t>732307</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>674963</t>
+          <t>732307</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1309375</t>
+          <t>1421934</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1309375</t>
+          <t>1421934</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1309375</t>
+          <t>1421934</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>123738</t>
+          <t>136667</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67443</t>
+          <t>115518</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>166310</t>
+          <t>161860</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>213764</t>
+          <t>237754</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>191483</t>
+          <t>215515</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>234656</t>
+          <t>260712</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>337503</t>
+          <t>374422</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>218522</t>
+          <t>344130</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>391624</t>
+          <t>409832</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>19,35%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1068157</t>
+          <t>911262</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1025585</t>
+          <t>886069</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1124452</t>
+          <t>932411</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>743696</t>
+          <t>832344</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>722804</t>
+          <t>809386</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>765977</t>
+          <t>854583</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1811852</t>
+          <t>1743605</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1757731</t>
+          <t>1708195</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1930833</t>
+          <t>1773897</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>83,75%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1191895</t>
+          <t>1047929</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1191895</t>
+          <t>1047929</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1191895</t>
+          <t>1047929</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>957460</t>
+          <t>1070098</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>957460</t>
+          <t>1070098</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>957460</t>
+          <t>1070098</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2149355</t>
+          <t>2118027</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2149355</t>
+          <t>2118027</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2149355</t>
+          <t>2118027</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>83488</t>
+          <t>93299</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67999</t>
+          <t>75341</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>103506</t>
+          <t>114247</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>138145</t>
+          <t>162991</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>66903</t>
+          <t>144214</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>184809</t>
+          <t>186896</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>221633</t>
+          <t>256290</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>150936</t>
+          <t>226174</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>264806</t>
+          <t>286886</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>17,76%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>621192</t>
+          <t>709774</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>601174</t>
+          <t>688826</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>636681</t>
+          <t>727732</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>795221</t>
+          <t>649268</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>748557</t>
+          <t>625363</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>866463</t>
+          <t>668045</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1416413</t>
+          <t>1359042</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1373240</t>
+          <t>1328446</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1487110</t>
+          <t>1389158</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>86,0%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>148613</t>
+          <t>160581</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>125663</t>
+          <t>137887</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>171436</t>
+          <t>184694</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>246550</t>
+          <t>270394</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>197951</t>
+          <t>244568</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>276533</t>
+          <t>297211</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>395163</t>
+          <t>430974</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>347550</t>
+          <t>398395</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>431815</t>
+          <t>467498</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>22,18%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>777202</t>
+          <t>828503</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>754379</t>
+          <t>804390</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>800152</t>
+          <t>851197</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>846043</t>
+          <t>847925</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>816060</t>
+          <t>821108</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>894642</t>
+          <t>873751</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1623245</t>
+          <t>1676429</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1586593</t>
+          <t>1639905</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1670858</t>
+          <t>1709008</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>81,1%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>925815</t>
+          <t>989084</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>925815</t>
+          <t>989084</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>925815</t>
+          <t>989084</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1092593</t>
+          <t>1118319</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1092593</t>
+          <t>1118319</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1092593</t>
+          <t>1118319</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2018408</t>
+          <t>2107403</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2018408</t>
+          <t>2107403</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2018408</t>
+          <t>2107403</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>442807</t>
+          <t>487850</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>340557</t>
+          <t>447367</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>491671</t>
+          <t>536492</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>752955</t>
+          <t>840688</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>619270</t>
+          <t>798390</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>825994</t>
+          <t>882710</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1195762</t>
+          <t>1328538</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1026657</t>
+          <t>1270891</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1294178</t>
+          <t>1389085</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3013995</t>
+          <t>3041864</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2965131</t>
+          <t>2993222</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3116245</t>
+          <t>3082347</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2905426</t>
+          <t>2892294</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2832387</t>
+          <t>2850272</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3039111</t>
+          <t>2934592</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5919422</t>
+          <t>5934158</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5821006</t>
+          <t>5873611</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6088527</t>
+          <t>5991805</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>82,5%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3456802</t>
+          <t>3529714</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3456802</t>
+          <t>3529714</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3456802</t>
+          <t>3529714</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3658381</t>
+          <t>3732982</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3658381</t>
+          <t>3732982</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3658381</t>
+          <t>3732982</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7115184</t>
+          <t>7262696</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7115184</t>
+          <t>7262696</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7115184</t>
+          <t>7262696</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
